--- a/artfynd/A 26692-2026 artfynd.xlsx
+++ b/artfynd/A 26692-2026 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>133925274</v>
       </c>
       <c r="B7" t="n">
-        <v>92532</v>
+        <v>92539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26692-2026 artfynd.xlsx
+++ b/artfynd/A 26692-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835109</v>
+        <v>133925274</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718565.8278003201</v>
+        <v>718451</v>
       </c>
       <c r="R2" t="n">
-        <v>7336529.041507859</v>
+        <v>7336417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +779,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91835125</v>
+        <v>91835137</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718573.9422224292</v>
+        <v>718061</v>
       </c>
       <c r="R3" t="n">
-        <v>7336519.072616779</v>
+        <v>7336637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,44 +881,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91835142</v>
+        <v>91835109</v>
       </c>
       <c r="B4" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718314.9368290943</v>
+        <v>718566</v>
       </c>
       <c r="R4" t="n">
-        <v>7336660.853141688</v>
+        <v>7336529</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,17 +978,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129688123</v>
+        <v>91835125</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,38 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718438</v>
+        <v>718574</v>
       </c>
       <c r="R5" t="n">
-        <v>7336636</v>
+        <v>7336519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,17 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,44 +1070,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129688122</v>
+        <v>129688123</v>
       </c>
       <c r="B6" t="n">
-        <v>80223</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1156,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718372</v>
+        <v>718438</v>
       </c>
       <c r="R6" t="n">
-        <v>7336434</v>
+        <v>7336636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,32 +1188,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133925274</v>
+        <v>129688122</v>
       </c>
       <c r="B7" t="n">
-        <v>92539</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1262,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718451</v>
+        <v>718372</v>
       </c>
       <c r="R7" t="n">
-        <v>7336417</v>
+        <v>7336434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,22 +1257,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1336,6 +1291,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91835142</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>718315</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7336661</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-10-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-10-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26692-2026 artfynd.xlsx
+++ b/artfynd/A 26692-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133925274</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835109</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688122</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,8 +1423,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>